--- a/naver-place-crawler/results_health/동구_PT.xlsx
+++ b/naver-place-crawler/results_health/동구_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,49 +559,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>카우짐 송림점</t>
+          <t>피티아시바</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dongdo0033@naver.com</t>
+          <t>unixgaseol7@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1454-7938</t>
+          <t>070-5255-5213</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 80 303호</t>
+          <t>인천광역시 동구 송림동</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/dw9626</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>457</v>
+        <v>0</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1970713518</t>
+          <t>1799811597</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1970713518</t>
+          <t>https://m.place.naver.com/place/1799811597</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>조짐</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jo-gym@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>032-777-9682</t>
+          <t>070-8932-2324</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수로 7 301호</t>
+          <t>인천광역시 동구 화수동</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jo-gym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1068496707</t>
+          <t>1708292189</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1068496707</t>
+          <t>https://m.place.naver.com/place/1708292189</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>온힘PT</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>onhim4477@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1441-4477</t>
+          <t>070-8039-8722</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 33 3층</t>
+          <t>인천광역시 동구 화수1.화평동</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/onhim4477</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2064548442</t>
+          <t>1705374816</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064548442</t>
+          <t>https://m.place.naver.com/place/1705374816</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,30 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>바디피티&amp;스킨뷰티</t>
+          <t>인싸짐 가좌점 24시연중무휴 PT 헬스장</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ydh5645sd@naver.com</t>
+          <t>wjdguss1045@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1376-3818</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 동구 수문통로 29 3층</t>
+          <t>인천광역시 서구 원적로 100 지하2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ydh5645sd</t>
+          <t>http://pf.kakao.com/_SxiUZG</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -879,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -890,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>1189</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>748</v>
       </c>
       <c r="R5" t="n">
-        <v>24</v>
+        <v>1937</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,42 +918,46 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13137004</t>
+          <t>1748758798</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13137004</t>
+          <t>https://m.place.naver.com/place/1748758798</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>몬스터PT</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dankkh418@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>070-8039-9883</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로43번길 29 (송림동) 몬스터PT</t>
+          <t>인천광역시 서구 가좌동</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -989,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,51 +1012,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1931268009</t>
+          <t>1018031898</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1931268009</t>
+          <t>https://m.place.naver.com/place/1018031898</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>팀메이크짐 헬스 PT 대전역점</t>
+          <t>포멀짐 헬스&amp;피티 제물포점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>meal10049@naver.com</t>
+          <t>formalgym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1349-6862</t>
+          <t>0507-1365-5941</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대전광역시 동구 동대전로46번길 7 5층 팀메이크</t>
+          <t>인천광역시 미추홀구 경인로 128 2층 포멀짐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/meal10049</t>
+          <t>https://blog.naver.com/formalgym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1266</v>
+        <v>102</v>
       </c>
       <c r="Q7" t="n">
-        <v>203</v>
+        <v>9</v>
       </c>
       <c r="R7" t="n">
-        <v>1469</v>
+        <v>111</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,51 +1106,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1576974587</t>
+          <t>1933593128</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1576974587</t>
+          <t>https://m.place.naver.com/place/1933593128</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 동구점</t>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>catess110@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1493-7680</t>
+          <t>070-8009-0489</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구 동구 안심로 266 4층</t>
+          <t>인천광역시 중구 선화동</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/catess110</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1152,12 +1160,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1173,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>766</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1313</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2079</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1200,6385 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>77223878</t>
+          <t>1430700696</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/77223878</t>
+          <t>https://m.place.naver.com/place/1430700696</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>국가대표 박인정 PT샵 주안본점</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>powerman962@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로325번길 27 미추홀더리브아파트 상가 2F</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pij_pt_shop</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>41</v>
+      </c>
+      <c r="R9" t="n">
+        <v>136</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1611506975</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1611506975</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>글로리트레이닝센터</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>seung1105-@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1418-4930</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 북항로32번안길 8 506호</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2015431625</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2015431625</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>070-8039-8720</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 창영동</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1037835069</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1037835069</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>온힘PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>onhim4477@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1441-4477</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 송현로 33 3층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/onhim4477</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>16</v>
+      </c>
+      <c r="R12" t="n">
+        <v>32</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2064548442</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2064548442</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>서인짐</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rlatjdls0305@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1384-9886</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 133 2층 서인짐</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rlatjdls0305</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>44</v>
+      </c>
+      <c r="R13" t="n">
+        <v>44</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1817968809</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1817968809</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>수디아필라테스프리미엄 2호점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sudiayogapilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1319-9682</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 송현로 24 상가 B동 2층 208호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sudiayogapilates</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+      <c r="R14" t="n">
+        <v>38</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1626857525</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1626857525</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>루트짐 주안점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>rlawnsgh3347@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1492-1172</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 석정로375번길 11 2층 루트짐 주안점</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rlawnsgh3347</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>72</v>
+      </c>
+      <c r="R15" t="n">
+        <v>132</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1765729791</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1765729791</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>카우짐 송림점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dongdo0033@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1454-7938</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 송림로 80 303호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/dw9626</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>157</v>
+      </c>
+      <c r="R16" t="n">
+        <v>457</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1970713518</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1970713518</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>070-8040-5383</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안동</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1889265333</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1889265333</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>유코치의슬림해짐</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>syhs007@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1465-4459</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 제일로 31 상가 2층 205호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yoocoach007</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>30</v>
+      </c>
+      <c r="R18" t="n">
+        <v>46</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1250104868</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1250104868</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CBBM휘트니스센타</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>csys026@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독정이로 40 4층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1707568333</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1707568333</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>070-8039-9870</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숭의동</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1205878365</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1205878365</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>도모 스트렝스</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5tokoda@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1334-7275</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 석정로 244 지하1층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@Domo_otokoda?si=vWR7lJmjGYe0J-VO</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>273</v>
+      </c>
+      <c r="R21" t="n">
+        <v>320</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1628768408</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628768408</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>라이프 P.T</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>mkj1104@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1366-6002</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 221 101동 214호</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2087474006</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2087474006</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>070-8039-8719</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 송현동</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1471027621</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1471027621</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>거뜬하다</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>gongju1432@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1371-4266</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 북항로32번안길 36 청라M골프 2층 헬스장</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>9</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1742455296</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1742455296</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>웅변,화술</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>jcomz7@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>070-8940-6264</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 송림동</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1088618869</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088618869</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>에이지트레이닝피티 주안점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ag_training@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1305-5338</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로325번길 27 3층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ag_training</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2007007809</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2007007809</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>웅변,화술</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>jcomz7@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>070-8934-1302</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 신흥동1가</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1605821182</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1605821182</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>진스 핏</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>jeansfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1399-8039</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 84 4층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jeans_fit77?igsh=cXg0ZTZ0N203emlt</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>43</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2036358510</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2036358510</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>전문건설업</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>비티아시바피티아시바이동식비계가설재판매임대설치</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>070-8055-2249</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 창영동</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1664508720</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1664508720</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>워라블짐 헬스 PT 도화점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>wlb1203@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1405-1273</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 251 3층 워라블짐</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wlb1203</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>235</v>
+      </c>
+      <c r="R30" t="n">
+        <v>385</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1596200279</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1596200279</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>페인트</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>피티상사</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>partnersdh@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 샛골로 136-1 1층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2034784321</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2034784321</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>웅변,화술</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>jcomz7@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>070-8931-8100</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가좌동</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1857339040</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1857339040</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>070-8082-0818</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 만석동</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1744427872</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1744427872</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>피티아시바</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>unixgaseol7@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>070-5255-9064</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가좌동</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1127060177</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1127060177</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>070-8068-4960</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 송현동</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1006757127</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1006757127</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>070-8075-9649</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 송림동</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1922639678</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1922639678</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>온핏</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>rlaqhqls3@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1301-5868</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 제물량로166번길 1-27 4층</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rlaqhqls3</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>30</v>
+      </c>
+      <c r="R37" t="n">
+        <v>39</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2071989754</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2071989754</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>올타임클래식짐 헬스PT 주안도화점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>all_time_classic@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1372-9682</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 한나루로 604 롯데월드타워오피스텔 B1층</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alltimeclassic_gym?igsh=cWV5d3BqdXF2MHI4&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>101</v>
+      </c>
+      <c r="R38" t="n">
+        <v>322</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2001570240</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2001570240</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>가좌동헬스장PT 니드트레이닝센터</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ntc_2017@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1408-8318</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 원적로 78 3층 303호니드트레이닝센터 (ntc2017)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ntc2017_obs</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>323</v>
+      </c>
+      <c r="R39" t="n">
+        <v>373</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>40729664</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/40729664</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>더블유닛</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>unit4579@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1370-4579</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 우현로 82-1 4층~5층 더블유닛</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/unit4579</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>741</v>
+      </c>
+      <c r="R40" t="n">
+        <v>798</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1895113732</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1895113732</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>웨이빗 피트니스 24시 헬스 PT 주안점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>weibit@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1328-8048</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 미추홀대로 716 6층 웨이빗 피트니스</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/weibit_official</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>2917</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>782</v>
+      </c>
+      <c r="R41" t="n">
+        <v>3699</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1700131075</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1700131075</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>070-8039-8721</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 화수동</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1832168408</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1832168408</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>와이키키짐 PT 주안점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>waikikigym2311@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1365-4408</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 미추홀대로 710 지하1층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/waikikigym_jwsong?igsh=bG51c2U5anlmZ2Ez&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1533</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1654</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1085067011</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1085067011</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>웅변,화술</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jcomz7@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>070-8935-9039</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안동</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1998758780</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1998758780</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>에이셉 트레이닝 센터</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>asap_hs@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1364-4608</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 개항로 69 3층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/swwTRafc</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>152</v>
+      </c>
+      <c r="R45" t="n">
+        <v>191</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1192923099</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1192923099</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>피티아시바</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>unixgaseol7@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>070-5255-2586</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 화수1.화평동</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1111897979</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1111897979</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>바디피티&amp;스킨뷰티</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ydh5645sd@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 수문통로 29 3층</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ydh5645sd</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>20</v>
+      </c>
+      <c r="R47" t="n">
+        <v>24</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>13137004</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13137004</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>JD휘트니스짐</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>balakas0101@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1408-9011</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 신포로27번길 3</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/balakas0101</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>42</v>
+      </c>
+      <c r="R48" t="n">
+        <v>72</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>16341034</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16341034</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>모두짐 재활PT 인천도화점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>modoo2206@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1484-5789</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숙골로87번길 28-1 다온1프라자 5층 모두짐 인천도화점</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@mutongweight</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>323</v>
+      </c>
+      <c r="R49" t="n">
+        <v>561</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1514606541</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1514606541</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>쎈 PT 스튜디오 인천도화점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ssenptstudio@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1362-0833</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숙골로87번길 2 센타프라자 203호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ssenptstudio</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>229</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>52</v>
+      </c>
+      <c r="R50" t="n">
+        <v>281</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1691655395</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1691655395</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>올스타짐 헬스 PT 도화점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>allstargym_dohwa@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1426-4489</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숙골로 93 로데오플라자 4층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_juCxmxj/chat</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>246</v>
+      </c>
+      <c r="R51" t="n">
+        <v>689</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1468509783</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1468509783</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>어테인휘트니스 헬스&amp;PT 석남점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>attain_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1337-3765</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 길주로 101-1 투썸플레이스건물 4층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/attain.fitness1/</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>353</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>519</v>
+      </c>
+      <c r="R52" t="n">
+        <v>872</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1639913680</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1639913680</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>넘버제로짐 헬스&amp;PT 주안역점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sid1287@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1363-2606</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 미추홀대로 725 5층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/no.0pt/</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>333</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>515</v>
+      </c>
+      <c r="R53" t="n">
+        <v>848</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1326633826</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1326633826</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>터닝포인트짐 헬스 PT 가좌점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>turningpointgym_gajw@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>032-576-1365</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 원적로 85 우신프라자 B1층 B01~B02호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/turningpointgym_gajw</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>538</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1549</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2087</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1588426455</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1588426455</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>몬스터PT</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>dankkh418@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 송림로43번길 29 (송림동) 몬스터PT</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>25</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1931268009</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1931268009</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>웅변,화술</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>jcomz7@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>070-8935-8172</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숭의동</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1359470432</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1359470432</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>웅변,화술</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>jcomz7@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>070-8935-9112</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 도원동</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1889289229</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1889289229</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>터닝포인트짐 헬스 PT 주안점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>tpg21@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1360-9997</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 미추홀대로 730 고려빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.tpgymjooan.com/</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>1151</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1396</v>
+      </c>
+      <c r="R58" t="n">
+        <v>2547</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1015443504</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1015443504</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>케이짐 인천도화점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>la4200@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1459-0283</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 염전로202번길 59 3층</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/la4200</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>43</v>
+      </c>
+      <c r="R59" t="n">
+        <v>66</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1115746281</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1115746281</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>수디아요가필라테스 동인천</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>sudiayogapilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1396-9683</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 송현로 30 4층 수디아 요가필라테스 동인천</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sudiayogapilates</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>531</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>209</v>
+      </c>
+      <c r="R60" t="n">
+        <v>740</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1388556375</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1388556375</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>주택전시관</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>두산위브더센트럴도화</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>drive023@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>070-8041-9638</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숭의동</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1980343684</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1980343684</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>070-8088-7806</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 화수1.화평동</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1421179794</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1421179794</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>조짐</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>jo-gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>032-777-9682</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 화수로 7 301호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jo-gym</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>66</v>
+      </c>
+      <c r="R63" t="n">
+        <v>108</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1068496707</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1068496707</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>여성전용 헬스 PT 바른습관PT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>hyptjuan@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1466-0535</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 염창로 65 여성전용 헬스 PT 바른습관PT</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mgm_hypt?igsh=ODA1NTc5OTg5Nw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>69</v>
+      </c>
+      <c r="R64" t="n">
+        <v>175</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1761795724</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1761795724</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>실내체육관</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>W GYM</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>mwgym2022@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>032-777-7749</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 송림로 138 미지빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>http://cafe.naver.com/7777749</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>19594091</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19594091</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>검사,분석,조사</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>삼영검사엔지니어링</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>activism9090@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>samyong@samyong.co.kr</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>032-888-8753</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 백범로934번길 10-14</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>http://www.samyong.co.kr/</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>35639490</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35639490</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>피트니스 연구소 용현점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>lfitness3@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1327-2357</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인주대로 68 예승프라자 4층, 5층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.fitnessinstitute.co.kr/</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>1728</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>724</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2452</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1279263313</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1279263313</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1:1 개인PT샵 팻번</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>gbw21@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>032-246-2158</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 건지로 375 5층 팻번</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gbw21</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>260</v>
+      </c>
+      <c r="R68" t="n">
+        <v>408</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1216515131</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1216515131</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>하프짐휘트니스 배다리점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>halfgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 송림로 24 6층</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/halfgym</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>343</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>51</v>
+      </c>
+      <c r="R69" t="n">
+        <v>394</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1222280711</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1222280711</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>웅변,화술</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>jcomz7@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>070-8935-6258</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 송현동</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1439213164</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1439213164</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>동익인간 원스텝짐_도화동 헬스장&amp;PT</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>godblessjiyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1420-5777</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숙골로95번길 19 영프라자3차 3층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/godblessjiyu</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>351</v>
+      </c>
+      <c r="R71" t="n">
+        <v>453</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1374352371</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1374352371</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>웅변,화술</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>jcomz7@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>070-8940-8832</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 도화동</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1336050744</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1336050744</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>기업</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>피티코리아</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>p-t-korea@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 보도진로73번길 8</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2142125524</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2142125524</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>수학교육</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PT수학교습소</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>realyjkim@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1378-6566</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숙골로88번길 46 상가동 203호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1491165182</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1491165182</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>웅변,화술</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>jcomz7@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>070-8934-5659</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>인천광역시 동구 만석동</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1837633354</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1837633354</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>바디에이프PT&amp;헬스 주안점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>apecompany@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1321-5947</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 석정로 430 3층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/apecompany</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>406</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>303</v>
+      </c>
+      <c r="R76" t="n">
+        <v>709</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1479770189</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1479770189</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/동구_PT.xlsx
+++ b/naver-place-crawler/results_health/동구_PT.xlsx
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피티아시바</t>
+          <t>온핏</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>unixgaseol7@naver.com</t>
+          <t>rlaqhqls3@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>070-5255-5213</t>
+          <t>0507-1301-5868</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림동</t>
+          <t>인천광역시 중구 제물량로166번길 1-27 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/rlaqhqls3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1799811597</t>
+          <t>2071989754</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1799811597</t>
+          <t>https://m.place.naver.com/place/2071989754</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>와이키키짐 PT 주안점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>waikikigym2311@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>070-8932-2324</t>
+          <t>0507-1365-4408</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수동</t>
+          <t>인천광역시 미추홀구 미추홀대로 710 지하1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/waikikigym_jwsong?igsh=bG51c2U5anlmZ2Ez&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1533</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1654</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1708292189</t>
+          <t>1085067011</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1708292189</t>
+          <t>https://m.place.naver.com/place/1085067011</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +747,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>에이셉 트레이닝 센터</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>asap_hs@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>070-8039-8722</t>
+          <t>0507-1364-4608</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수1.화평동</t>
+          <t>인천광역시 중구 개항로 69 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/swwTRafc</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -800,22 +800,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1705374816</t>
+          <t>1192923099</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1705374816</t>
+          <t>https://m.place.naver.com/place/1192923099</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -841,44 +841,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>인싸짐 가좌점 24시연중무휴 PT 헬스장</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wjdguss1045@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1376-3818</t>
+          <t>070-8039-8722</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 100 지하2층</t>
+          <t>인천광역시 동구 화수1.화평동</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_SxiUZG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -894,22 +894,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1189</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>748</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1937</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1748758798</t>
+          <t>1705374816</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1748758798</t>
+          <t>https://m.place.naver.com/place/1705374816</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -935,34 +935,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>워라블짐 헬스 PT 도화점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>wlb1203@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>070-8039-9883</t>
+          <t>0507-1405-1273</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가좌동</t>
+          <t>인천광역시 미추홀구 경인로 251 3층 워라블짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wlb1203</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1018031898</t>
+          <t>1596200279</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1018031898</t>
+          <t>https://m.place.naver.com/place/1596200279</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1029,34 +1029,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>포멀짐 헬스&amp;피티 제물포점</t>
+          <t>동익인간 원스텝짐_도화동 헬스장&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>formalgym@naver.com</t>
+          <t>godblessjiyu@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1365-5941</t>
+          <t>0507-1420-5777</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 128 2층 포멀짐</t>
+          <t>인천광역시 미추홀구 숙골로95번길 19 영프라자3차 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/formalgym</t>
+          <t>https://blog.naver.com/godblessjiyu</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1094,10 +1094,10 @@
         <v>102</v>
       </c>
       <c r="Q7" t="n">
-        <v>9</v>
+        <v>351</v>
       </c>
       <c r="R7" t="n">
-        <v>111</v>
+        <v>453</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1933593128</t>
+          <t>1374352371</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1933593128</t>
+          <t>https://m.place.naver.com/place/1374352371</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,29 +1123,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+          <t>거뜬하다</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>gongju1432@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>070-8009-0489</t>
+          <t>0507-1371-4266</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 중구 선화동</t>
+          <t>인천광역시 서구 북항로32번안길 36 청라M골프 2층 헬스장</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1430700696</t>
+          <t>1742455296</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430700696</t>
+          <t>https://m.place.naver.com/place/1742455296</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,25 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>국가대표 박인정 PT샵 주안본점</t>
+          <t>라이프 P.T</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>powerman962@naver.com</t>
+          <t>mkj1104@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1366-6002</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로325번길 27 미추홀더리브아파트 상가 2F</t>
+          <t>인천광역시 미추홀구 경인로 221 101동 214호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pij_pt_shop</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1250,7 +1254,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1271,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1611506975</t>
+          <t>2087474006</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611506975</t>
+          <t>https://m.place.naver.com/place/2087474006</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1307,29 +1311,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>글로리트레이닝센터</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>seung1105-@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1418-4930</t>
+          <t>070-8931-8100</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 북항로32번안길 8 506호</t>
+          <t>인천광역시 서구 가좌동</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1372,10 +1376,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2015431625</t>
+          <t>1857339040</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015431625</t>
+          <t>https://m.place.naver.com/place/1857339040</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1401,44 +1405,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>터닝포인트짐 헬스 PT 주안점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>tpg21@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>070-8039-8720</t>
+          <t>0507-1360-9997</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 동구 창영동</t>
+          <t>인천광역시 미추홀구 미추홀대로 730 고려빌딩 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.tpgymjooan.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1454,22 +1458,22 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1150</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1397</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2547</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1037835069</t>
+          <t>1015443504</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037835069</t>
+          <t>https://m.place.naver.com/place/1015443504</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1500,29 +1504,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>온힘PT</t>
+          <t>넘버제로짐 헬스&amp;PT 주안역점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>onhim4477@naver.com</t>
+          <t>sid1287@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1441-4477</t>
+          <t>0507-1363-2606</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 33 3층</t>
+          <t>인천광역시 미추홀구 미추홀대로 725 5층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/onhim4477</t>
+          <t>https://www.instagram.com/no.0pt/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1537,7 +1541,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1557,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>16</v>
+        <v>333</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>515</v>
       </c>
       <c r="R12" t="n">
-        <v>32</v>
+        <v>848</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,12 +1576,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2064548442</t>
+          <t>1326633826</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064548442</t>
+          <t>https://m.place.naver.com/place/1326633826</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1594,29 +1598,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>서인짐</t>
+          <t>터닝포인트짐 헬스 PT 가좌점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rlatjdls0305@naver.com</t>
+          <t>turningpointgym_gajw@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1384-9886</t>
+          <t>032-576-1365</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 133 2층 서인짐</t>
+          <t>인천광역시 서구 원적로 85 우신프라자 B1층 B01~B02호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlatjdls0305</t>
+          <t>https://blog.naver.com/turningpointgym_gajw</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1647,17 +1651,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="Q13" t="n">
-        <v>44</v>
+        <v>1549</v>
       </c>
       <c r="R13" t="n">
-        <v>44</v>
+        <v>2087</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,12 +1670,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1817968809</t>
+          <t>1588426455</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817968809</t>
+          <t>https://m.place.naver.com/place/1588426455</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1683,39 +1687,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>수디아필라테스프리미엄 2호점</t>
+          <t>인싸짐 가좌점 24시연중무휴 PT 헬스장</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sudiayogapilates@naver.com</t>
+          <t>wjdguss1045@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1319-9682</t>
+          <t>0507-1376-3818</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 24 상가 B동 2층 208호</t>
+          <t>인천광역시 서구 원적로 100 지하2층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sudiayogapilates</t>
+          <t>http://pf.kakao.com/_SxiUZG</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1725,7 +1729,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1736,7 +1740,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1745,13 +1749,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>23</v>
+        <v>1189</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>748</v>
       </c>
       <c r="R14" t="n">
-        <v>38</v>
+        <v>1937</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,12 +1764,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1626857525</t>
+          <t>1748758798</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626857525</t>
+          <t>https://m.place.naver.com/place/1748758798</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1782,29 +1786,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>루트짐 주안점</t>
+          <t>유코치의슬림해짐</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rlawnsgh3347@naver.com</t>
+          <t>syhs007@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1492-1172</t>
+          <t>0507-1465-4459</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로375번길 11 2층 루트짐 주안점</t>
+          <t>인천광역시 미추홀구 제일로 31 상가 2층 205호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlawnsgh3347</t>
+          <t>https://www.instagram.com/yoocoach007</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1819,7 +1823,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1830,7 +1834,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1839,13 +1843,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="Q15" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="R15" t="n">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,12 +1858,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1765729791</t>
+          <t>1250104868</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1765729791</t>
+          <t>https://m.place.naver.com/place/1250104868</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1871,49 +1875,49 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>카우짐 송림점</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dongdo0033@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1454-7938</t>
+          <t>070-8935-9039</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 80 303호</t>
+          <t>인천광역시 미추홀구 주안동</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/dw9626</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1929,17 +1933,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>457</v>
+        <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,12 +1952,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1970713518</t>
+          <t>1998758780</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1970713518</t>
+          <t>https://m.place.naver.com/place/1998758780</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1965,34 +1969,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
+          <t>수디아필라테스프리미엄 2호점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rodtmdu12@naver.com</t>
+          <t>sudiayogapilates@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>070-8040-5383</t>
+          <t>0507-1319-9682</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안동</t>
+          <t>인천광역시 동구 송현로 24 상가 B동 2층 208호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sudiayogapilates</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2002,12 +2006,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2023,17 +2027,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,12 +2046,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1889265333</t>
+          <t>1626857525</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1889265333</t>
+          <t>https://m.place.naver.com/place/1626857525</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2064,29 +2068,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>유코치의슬림해짐</t>
+          <t>루트짐 주안점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>syhs007@naver.com</t>
+          <t>rlawnsgh3347@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1465-4459</t>
+          <t>0507-1492-1172</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 제일로 31 상가 2층 205호</t>
+          <t>인천광역시 미추홀구 석정로375번길 11 2층 루트짐 주안점</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yoocoach007</t>
+          <t>https://blog.naver.com/rlawnsgh3347</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2101,7 +2105,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2112,7 +2116,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2121,13 +2125,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="Q18" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="R18" t="n">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,12 +2140,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1250104868</t>
+          <t>1765729791</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1250104868</t>
+          <t>https://m.place.naver.com/place/1765729791</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2153,30 +2157,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CBBM휘트니스센타</t>
+          <t>진스 핏</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>csys026@naver.com</t>
+          <t>jeansfit@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1399-8039</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독정이로 40 4층</t>
+          <t>인천광역시 미추홀구 경인로 84 4층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jeans_fit77?igsh=cXg0ZTZ0N203emlt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2186,7 +2194,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2207,17 +2215,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q19" t="n">
         <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,12 +2234,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1707568333</t>
+          <t>2036358510</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1707568333</t>
+          <t>https://m.place.naver.com/place/2036358510</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2243,34 +2251,30 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>하프짐휘트니스 배다리점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>halfgym@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>070-8039-9870</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숭의동</t>
+          <t>인천광역시 동구 송림로 24 6층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/halfgym</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2280,12 +2284,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2305,13 +2309,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,12 +2324,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1205878365</t>
+          <t>1222280711</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1205878365</t>
+          <t>https://m.place.naver.com/place/1222280711</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2337,34 +2341,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>실내체육관</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>도모 스트렝스</t>
+          <t>W GYM</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5tokoda@naver.com</t>
+          <t>mwgym2022@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1334-7275</t>
+          <t>032-777-7749</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로 244 지하1층</t>
+          <t>인천광역시 동구 송림로 138 미지빌딩 3층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://youtube.com/@Domo_otokoda?si=vWR7lJmjGYe0J-VO</t>
+          <t>http://cafe.naver.com/7777749</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2379,7 +2383,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2395,17 +2399,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>273</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>320</v>
+        <v>2</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,12 +2418,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1628768408</t>
+          <t>19594091</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628768408</t>
+          <t>https://m.place.naver.com/place/19594091</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2436,29 +2440,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>라이프 P.T</t>
+          <t>더블유닛</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mkj1104@naver.com</t>
+          <t>unit4579@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1366-6002</t>
+          <t>0507-1370-4579</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 221 101동 214호</t>
+          <t>인천광역시 중구 우현로 82-1 4층~5층 더블유닛</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/unit4579</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2468,12 +2472,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2489,17 +2493,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>741</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>798</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,12 +2512,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2087474006</t>
+          <t>1895113732</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087474006</t>
+          <t>https://m.place.naver.com/place/1895113732</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2525,49 +2529,49 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>카우짐 송림점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>dongdo0033@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>070-8039-8719</t>
+          <t>0507-1454-7938</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현동</t>
+          <t>인천광역시 동구 송림로 80 303호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://link.inpock.co.kr/dw9626</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2583,17 +2587,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,12 +2606,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1471027621</t>
+          <t>1970713518</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471027621</t>
+          <t>https://m.place.naver.com/place/1970713518</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2619,29 +2623,29 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>거뜬하다</t>
+          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>gongju1432@naver.com</t>
+          <t>rodtmdu12@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1371-4266</t>
+          <t>070-8088-7806</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 서구 북항로32번안길 36 청라M골프 2층 헬스장</t>
+          <t>인천광역시 동구 화수1.화평동</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2681,13 +2685,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,12 +2700,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1742455296</t>
+          <t>1421179794</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742455296</t>
+          <t>https://m.place.naver.com/place/1421179794</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2713,34 +2717,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>웨이빗 피트니스 24시 헬스 PT 주안점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>weibit@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>070-8940-6264</t>
+          <t>0507-1328-8048</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림동</t>
+          <t>인천광역시 미추홀구 미추홀대로 716 6층 웨이빗 피트니스</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/weibit_official</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2750,7 +2754,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2771,17 +2775,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2917</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>782</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3699</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,12 +2794,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1088618869</t>
+          <t>1700131075</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088618869</t>
+          <t>https://m.place.naver.com/place/1700131075</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2807,34 +2811,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에이지트레이닝피티 주안점</t>
+          <t>글로리트레이닝센터</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ag_training@naver.com</t>
+          <t>seung1105-@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1305-5338</t>
+          <t>0507-1418-4930</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로325번길 27 3층</t>
+          <t>인천광역시 서구 북항로32번안길 8 506호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ag_training</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2844,12 +2848,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2865,17 +2869,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2884,12 +2888,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2007007809</t>
+          <t>2015431625</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007007809</t>
+          <t>https://m.place.naver.com/place/2015431625</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2917,13 +2921,13 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>070-8934-1302</t>
+          <t>070-8940-8832</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 중구 신흥동1가</t>
+          <t>인천광역시 미추홀구 도화동</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2978,12 +2982,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1605821182</t>
+          <t>1336050744</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1605821182</t>
+          <t>https://m.place.naver.com/place/1336050744</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2995,34 +2999,34 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>진스 핏</t>
+          <t>케이짐 인천도화점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jeansfit@naver.com</t>
+          <t>la4200@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1399-8039</t>
+          <t>0507-1459-0283</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 84 4층</t>
+          <t>인천광역시 미추홀구 염전로202번길 59 3층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jeans_fit77?igsh=cXg0ZTZ0N203emlt</t>
+          <t>https://blog.naver.com/la4200</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3037,7 +3041,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3057,13 +3061,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="R28" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3072,12 +3076,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2036358510</t>
+          <t>1115746281</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036358510</t>
+          <t>https://m.place.naver.com/place/1115746281</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3089,34 +3093,34 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>전문건설업</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>비티아시바피티아시바이동식비계가설재판매임대설치</t>
+          <t>어테인휘트니스 헬스&amp;PT 석남점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>attain_fitness@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>070-8055-2249</t>
+          <t>0507-1337-3765</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 동구 창영동</t>
+          <t>인천광역시 서구 길주로 101-1 투썸플레이스건물 4층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/attain.fitness1/</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3126,7 +3130,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3142,22 +3146,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3166,12 +3170,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1664508720</t>
+          <t>1639913680</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1664508720</t>
+          <t>https://m.place.naver.com/place/1639913680</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3183,34 +3187,34 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>워라블짐 헬스 PT 도화점</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>wlb1203@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1405-1273</t>
+          <t>070-8039-9870</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 251 3층 워라블짐</t>
+          <t>인천광역시 미추홀구 숭의동</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wlb1203</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3220,12 +3224,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3241,17 +3245,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3260,12 +3264,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1596200279</t>
+          <t>1205878365</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596200279</t>
+          <t>https://m.place.naver.com/place/1205878365</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3277,25 +3281,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>페인트</t>
+          <t>수학교육</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>피티상사</t>
+          <t>PT수학교습소</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>partnersdh@naver.com</t>
+          <t>realyjkim@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1378-6566</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로 136-1 1층</t>
+          <t>인천광역시 미추홀구 숙골로88번길 46 상가동 203호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3338,10 +3346,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3350,12 +3358,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2034784321</t>
+          <t>1491165182</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2034784321</t>
+          <t>https://m.place.naver.com/place/1491165182</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3367,29 +3375,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>070-8931-8100</t>
+          <t>070-8082-0818</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가좌동</t>
+          <t>인천광역시 동구 만석동</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3429,13 +3437,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3444,12 +3452,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1857339040</t>
+          <t>1744427872</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1857339040</t>
+          <t>https://m.place.naver.com/place/1744427872</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3461,34 +3469,34 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+          <t>모두짐 재활PT 인천도화점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>modoo2206@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>070-8082-0818</t>
+          <t>0507-1484-5789</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 동구 만석동</t>
+          <t>인천광역시 미추홀구 숙골로87번길 28-1 다온1프라자 5층 모두짐 인천도화점</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@mutongweight</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3498,7 +3506,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3519,17 +3527,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>238</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>561</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3538,12 +3546,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1744427872</t>
+          <t>1514606541</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1744427872</t>
+          <t>https://m.place.naver.com/place/1514606541</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3555,29 +3563,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>피티아시바</t>
+          <t>몬스터PT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>unixgaseol7@naver.com</t>
+          <t>dankkh418@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>070-5255-9064</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가좌동</t>
+          <t>인천광역시 동구 송림로43번길 29 (송림동) 몬스터PT</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3617,13 +3621,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3632,12 +3636,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1127060177</t>
+          <t>1931268009</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1127060177</t>
+          <t>https://m.place.naver.com/place/1931268009</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3649,34 +3653,34 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+          <t>여성전용 헬스 PT 바른습관PT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>hyptjuan@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>070-8068-4960</t>
+          <t>0507-1466-0535</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현동</t>
+          <t>인천광역시 미추홀구 염창로 65 여성전용 헬스 PT 바른습관PT</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mgm_hypt?igsh=ODA1NTc5OTg5Nw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3686,7 +3690,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3707,17 +3711,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3726,12 +3730,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1006757127</t>
+          <t>1761795724</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1006757127</t>
+          <t>https://m.place.naver.com/place/1761795724</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3743,29 +3747,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>페인트</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+          <t>피티상사</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>partnersdh@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>070-8075-9649</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림동</t>
+          <t>인천광역시 동구 샛골로 136-1 1층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3808,10 +3808,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1922639678</t>
+          <t>2034784321</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1922639678</t>
+          <t>https://m.place.naver.com/place/2034784321</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3837,34 +3837,34 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>온핏</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>rlaqhqls3@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1301-5868</t>
+          <t>070-8935-8172</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 중구 제물량로166번길 1-27 4층</t>
+          <t>인천광역시 미추홀구 숭의동</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlaqhqls3</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2071989754</t>
+          <t>1359470432</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2071989754</t>
+          <t>https://m.place.naver.com/place/1359470432</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3936,34 +3936,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>올타임클래식짐 헬스PT 주안도화점</t>
+          <t>피트니스 연구소 용현점 헬스 PT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>all_time_classic@naver.com</t>
+          <t>lfitness3@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1372-9682</t>
+          <t>0507-1327-2357</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로 604 롯데월드타워오피스텔 B1층</t>
+          <t>인천광역시 미추홀구 인주대로 68 예승프라자 4층, 5층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/alltimeclassic_gym?igsh=cWV5d3BqdXF2MHI4&amp;utm_source=qr</t>
+          <t>https://www.fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3984,7 +3984,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3993,13 +3993,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>221</v>
+        <v>1728</v>
       </c>
       <c r="Q38" t="n">
-        <v>101</v>
+        <v>726</v>
       </c>
       <c r="R38" t="n">
-        <v>322</v>
+        <v>2454</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,12 +4008,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2001570240</t>
+          <t>1279263313</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001570240</t>
+          <t>https://m.place.naver.com/place/1279263313</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4025,34 +4025,34 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>가좌동헬스장PT 니드트레이닝센터</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ntc_2017@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1408-8318</t>
+          <t>070-8039-8721</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 78 3층 303호니드트레이닝센터 (ntc2017)</t>
+          <t>인천광역시 동구 화수동</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ntc2017_obs</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4083,17 +4083,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,12 +4102,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>40729664</t>
+          <t>1832168408</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/40729664</t>
+          <t>https://m.place.naver.com/place/1832168408</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4119,34 +4119,34 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>더블유닛</t>
+          <t>올타임클래식짐 헬스PT 주안도화점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>unit4579@naver.com</t>
+          <t>all_time_classic@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1370-4579</t>
+          <t>0507-1372-9682</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로 82-1 4층~5층 더블유닛</t>
+          <t>인천광역시 미추홀구 한나루로 604 롯데월드타워오피스텔 B1층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unit4579</t>
+          <t>https://www.instagram.com/alltimeclassic_gym?igsh=cWV5d3BqdXF2MHI4&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4181,13 +4181,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>57</v>
+        <v>221</v>
       </c>
       <c r="Q40" t="n">
-        <v>741</v>
+        <v>101</v>
       </c>
       <c r="R40" t="n">
-        <v>798</v>
+        <v>322</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,12 +4196,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1895113732</t>
+          <t>2001570240</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895113732</t>
+          <t>https://m.place.naver.com/place/2001570240</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4213,34 +4213,30 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>기업</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>웨이빗 피트니스 24시 헬스 PT 주안점</t>
+          <t>피티코리아</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>weibit@naver.com</t>
+          <t>p-t-korea@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1328-8048</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 716 6층 웨이빗 피트니스</t>
+          <t>인천광역시 서구 보도진로73번길 8</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/weibit_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4250,7 +4246,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4271,17 +4267,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2917</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>782</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3699</v>
+        <v>0</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4290,12 +4286,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1700131075</t>
+          <t>2142125524</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1700131075</t>
+          <t>https://m.place.naver.com/place/2142125524</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4307,34 +4303,34 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>서인짐</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>rlatjdls0305@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>070-8039-8721</t>
+          <t>0507-1384-9886</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수동</t>
+          <t>인천광역시 미추홀구 경인로 133 2층 서인짐</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/rlatjdls0305</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4344,12 +4340,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4372,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4384,12 +4380,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1832168408</t>
+          <t>1817968809</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1832168408</t>
+          <t>https://m.place.naver.com/place/1817968809</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4406,29 +4402,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>와이키키짐 PT 주안점</t>
+          <t>가좌동헬스장PT 니드트레이닝센터</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>waikikigym2311@naver.com</t>
+          <t>ntc_2017@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1365-4408</t>
+          <t>0507-1408-8318</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 710 지하1층</t>
+          <t>인천광역시 서구 원적로 78 3층 303호니드트레이닝센터 (ntc2017)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/waikikigym_jwsong?igsh=bG51c2U5anlmZ2Ez&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/ntc2017_obs</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4463,13 +4459,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="Q43" t="n">
-        <v>1533</v>
+        <v>323</v>
       </c>
       <c r="R43" t="n">
-        <v>1654</v>
+        <v>373</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4478,12 +4474,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1085067011</t>
+          <t>40729664</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1085067011</t>
+          <t>https://m.place.naver.com/place/40729664</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4495,23 +4491,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>rodtmdu12@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>070-8935-9039</t>
+          <t>070-8040-5383</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -4572,12 +4568,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1998758780</t>
+          <t>1889265333</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1998758780</t>
+          <t>https://m.place.naver.com/place/1889265333</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4589,34 +4585,34 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>에이셉 트레이닝 센터</t>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>asap_hs@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1364-4608</t>
+          <t>070-8009-0489</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 중구 개항로 69 3층</t>
+          <t>인천광역시 중구 선화동</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/swwTRafc</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4626,7 +4622,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4642,22 +4638,22 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4666,12 +4662,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1192923099</t>
+          <t>1430700696</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192923099</t>
+          <t>https://m.place.naver.com/place/1430700696</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4683,34 +4679,34 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>피티아시바</t>
+          <t>온힘PT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>unixgaseol7@naver.com</t>
+          <t>onhim4477@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>070-5255-2586</t>
+          <t>0507-1441-4477</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수1.화평동</t>
+          <t>인천광역시 동구 송현로 33 3층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/onhim4477</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4720,12 +4716,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4741,17 +4737,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4760,12 +4756,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1111897979</t>
+          <t>2064548442</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1111897979</t>
+          <t>https://m.place.naver.com/place/2064548442</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4867,34 +4863,34 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JD휘트니스짐</t>
+          <t>피티아시바</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>balakas0101@naver.com</t>
+          <t>unixgaseol7@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1408-9011</t>
+          <t>070-5255-2586</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 중구 신포로27번길 3</t>
+          <t>인천광역시 동구 화수1.화평동</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/balakas0101</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4904,12 +4900,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4925,17 +4921,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4944,12 +4940,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>16341034</t>
+          <t>1111897979</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16341034</t>
+          <t>https://m.place.naver.com/place/1111897979</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4966,29 +4962,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>모두짐 재활PT 인천도화점</t>
+          <t>국가대표 박인정 PT샵 주안본점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>modoo2206@naver.com</t>
+          <t>powerman962@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0507-1484-5789</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 28-1 다온1프라자 5층 모두짐 인천도화점</t>
+          <t>인천광역시 미추홀구 경인로325번길 27 미추홀더리브아파트 상가 2F</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://youtube.com/@mutongweight</t>
+          <t>https://www.instagram.com/pij_pt_shop</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5023,13 +5015,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>238</v>
+        <v>95</v>
       </c>
       <c r="Q49" t="n">
-        <v>323</v>
+        <v>41</v>
       </c>
       <c r="R49" t="n">
-        <v>561</v>
+        <v>136</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5038,12 +5030,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1514606541</t>
+          <t>1611506975</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1514606541</t>
+          <t>https://m.place.naver.com/place/1611506975</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5055,39 +5047,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>쎈 PT 스튜디오 인천도화점</t>
+          <t>올스타짐 헬스 PT 도화점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ssenptstudio@naver.com</t>
+          <t>allstargym_dohwa@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1362-0833</t>
+          <t>0507-1426-4489</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 2 센타프라자 203호</t>
+          <t>인천광역시 미추홀구 숙골로 93 로데오플라자 4층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssenptstudio</t>
+          <t>http://pf.kakao.com/_juCxmxj/chat</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5097,7 +5089,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5117,13 +5109,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>229</v>
+        <v>443</v>
       </c>
       <c r="Q50" t="n">
-        <v>52</v>
+        <v>246</v>
       </c>
       <c r="R50" t="n">
-        <v>281</v>
+        <v>689</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5132,12 +5124,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1691655395</t>
+          <t>1468509783</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1691655395</t>
+          <t>https://m.place.naver.com/place/1468509783</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5149,39 +5141,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>올스타짐 헬스 PT 도화점</t>
+          <t>쎈 PT 스튜디오 인천도화점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>allstargym_dohwa@naver.com</t>
+          <t>ssenptstudio@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1426-4489</t>
+          <t>0507-1362-0833</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로 93 로데오플라자 4층</t>
+          <t>인천광역시 미추홀구 숙골로87번길 2 센타프라자 203호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_juCxmxj/chat</t>
+          <t>https://blog.naver.com/ssenptstudio</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5191,7 +5183,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5211,13 +5203,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>443</v>
+        <v>229</v>
       </c>
       <c r="Q51" t="n">
-        <v>246</v>
+        <v>52</v>
       </c>
       <c r="R51" t="n">
-        <v>689</v>
+        <v>281</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5226,12 +5218,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1468509783</t>
+          <t>1691655395</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1468509783</t>
+          <t>https://m.place.naver.com/place/1691655395</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5248,29 +5240,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>어테인휘트니스 헬스&amp;PT 석남점</t>
+          <t>JD휘트니스짐</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>attain_fitness@naver.com</t>
+          <t>balakas0101@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1337-3765</t>
+          <t>0507-1408-9011</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 서구 길주로 101-1 투썸플레이스건물 4층</t>
+          <t>인천광역시 중구 신포로27번길 3</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/attain.fitness1/</t>
+          <t>https://blog.naver.com/balakas0101</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5285,7 +5277,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5296,7 +5288,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5305,13 +5297,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>353</v>
+        <v>30</v>
       </c>
       <c r="Q52" t="n">
-        <v>519</v>
+        <v>42</v>
       </c>
       <c r="R52" t="n">
-        <v>872</v>
+        <v>72</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5320,12 +5312,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1639913680</t>
+          <t>16341034</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1639913680</t>
+          <t>https://m.place.naver.com/place/16341034</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5337,34 +5329,34 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>넘버제로짐 헬스&amp;PT 주안역점</t>
+          <t>피티아시바</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>sid1287@naver.com</t>
+          <t>unixgaseol7@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1363-2606</t>
+          <t>070-5255-5213</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 725 5층</t>
+          <t>인천광역시 동구 송림동</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/no.0pt/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5374,7 +5366,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5395,17 +5387,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5414,12 +5406,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1326633826</t>
+          <t>1799811597</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1326633826</t>
+          <t>https://m.place.naver.com/place/1799811597</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5431,34 +5423,34 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT 가좌점</t>
+          <t>피티아시바</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>turningpointgym_gajw@naver.com</t>
+          <t>unixgaseol7@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>032-576-1365</t>
+          <t>070-5255-9064</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 85 우신프라자 B1층 B01~B02호</t>
+          <t>인천광역시 서구 가좌동</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/turningpointgym_gajw</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5468,12 +5460,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5489,17 +5481,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>538</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>1549</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2087</v>
+        <v>0</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5508,12 +5500,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1588426455</t>
+          <t>1127060177</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1588426455</t>
+          <t>https://m.place.naver.com/place/1127060177</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5530,25 +5522,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>몬스터PT</t>
+          <t>도모 스트렝스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>dankkh418@naver.com</t>
+          <t>5tokoda@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1334-7275</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로43번길 29 (송림동) 몬스터PT</t>
+          <t>인천광역시 미추홀구 석정로 244 지하1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@Domo_otokoda?si=vWR7lJmjGYe0J-VO</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5558,7 +5554,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5579,17 +5575,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>273</v>
       </c>
       <c r="R55" t="n">
-        <v>25</v>
+        <v>320</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5598,12 +5594,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1931268009</t>
+          <t>1628768408</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1931268009</t>
+          <t>https://m.place.naver.com/place/1628768408</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5631,13 +5627,13 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>070-8935-8172</t>
+          <t>070-8940-6264</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숭의동</t>
+          <t>인천광역시 동구 송림동</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5692,12 +5688,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1359470432</t>
+          <t>1088618869</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1359470432</t>
+          <t>https://m.place.naver.com/place/1088618869</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5709,29 +5705,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>CBBM휘트니스센타</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>csys026@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>070-8935-9112</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 중구 도원동</t>
+          <t>인천광역시 미추홀구 독정이로 40 4층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5771,13 +5763,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5786,12 +5778,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1889289229</t>
+          <t>1707568333</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1889289229</t>
+          <t>https://m.place.naver.com/place/1707568333</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5803,44 +5795,44 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT 주안점</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>tpg21@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1360-9997</t>
+          <t>070-8039-8720</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 730 고려빌딩 4층</t>
+          <t>인천광역시 동구 창영동</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tpgymjooan.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5856,22 +5848,22 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1151</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>1396</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2547</v>
+        <v>0</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5880,12 +5872,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1015443504</t>
+          <t>1037835069</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1015443504</t>
+          <t>https://m.place.naver.com/place/1037835069</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5897,34 +5889,34 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>케이짐 인천도화점</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>la4200@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1459-0283</t>
+          <t>070-8932-2324</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 59 3층</t>
+          <t>인천광역시 동구 화수동</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/la4200</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5934,12 +5926,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5955,17 +5947,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5974,12 +5966,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1115746281</t>
+          <t>1708292189</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1115746281</t>
+          <t>https://m.place.naver.com/place/1708292189</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5991,34 +5983,34 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>수디아요가필라테스 동인천</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sudiayogapilates@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1396-9683</t>
+          <t>070-8935-9112</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 30 4층 수디아 요가필라테스 동인천</t>
+          <t>인천광역시 중구 도원동</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sudiayogapilates</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6028,12 +6020,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6049,17 +6041,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>531</v>
+        <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>740</v>
+        <v>1</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6068,12 +6060,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1388556375</t>
+          <t>1889289229</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1388556375</t>
+          <t>https://m.place.naver.com/place/1889289229</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6085,29 +6077,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>주택전시관</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>두산위브더센트럴도화</t>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>drive023@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>070-8041-9638</t>
+          <t>070-8068-4960</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숭의동</t>
+          <t>인천광역시 동구 송현동</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6150,10 +6142,10 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6162,12 +6154,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1980343684</t>
+          <t>1006757127</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1980343684</t>
+          <t>https://m.place.naver.com/place/1006757127</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6179,29 +6171,29 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>전문건설업</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
+          <t>비티아시바피티아시바이동식비계가설재판매임대설치</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>rodtmdu12@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>070-8088-7806</t>
+          <t>070-8055-2249</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수1.화평동</t>
+          <t>인천광역시 동구 창영동</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6256,12 +6248,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1421179794</t>
+          <t>1664508720</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421179794</t>
+          <t>https://m.place.naver.com/place/1664508720</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6273,34 +6265,38 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>검사,분석,조사</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>조짐</t>
+          <t>삼영검사엔지니어링</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jo-gym@naver.com</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>activism9090@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>samyong@samyong.co.kr</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>032-777-9682</t>
+          <t>032-888-8753</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수로 7 301호</t>
+          <t>인천광역시 서구 백범로934번길 10-14</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jo-gym</t>
+          <t>http://www.samyong.co.kr/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6315,7 +6311,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6335,13 +6331,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6350,12 +6346,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1068496707</t>
+          <t>35639490</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1068496707</t>
+          <t>https://m.place.naver.com/place/35639490</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6367,34 +6363,34 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>여성전용 헬스 PT 바른습관PT</t>
+          <t>수디아요가필라테스 동인천</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>hyptjuan@naver.com</t>
+          <t>sudiayogapilates@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1466-0535</t>
+          <t>0507-1396-9683</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염창로 65 여성전용 헬스 PT 바른습관PT</t>
+          <t>인천광역시 동구 송현로 30 4층 수디아 요가필라테스 동인천</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mgm_hypt?igsh=ODA1NTc5OTg5Nw%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/sudiayogapilates</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6409,7 +6405,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6429,13 +6425,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>106</v>
+        <v>531</v>
       </c>
       <c r="Q64" t="n">
-        <v>69</v>
+        <v>209</v>
       </c>
       <c r="R64" t="n">
-        <v>175</v>
+        <v>740</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6444,12 +6440,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1761795724</t>
+          <t>1388556375</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1761795724</t>
+          <t>https://m.place.naver.com/place/1388556375</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6461,34 +6457,34 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>실내체육관</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>W GYM</t>
+          <t>1:1 개인PT샵 팻번</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>mwgym2022@naver.com</t>
+          <t>gbw21@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>032-777-7749</t>
+          <t>032-246-2158</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 138 미지빌딩 3층</t>
+          <t>인천광역시 서구 건지로 375 5층 팻번</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>http://cafe.naver.com/7777749</t>
+          <t>https://blog.naver.com/gbw21</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6519,17 +6515,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1</v>
+        <v>148</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="R65" t="n">
-        <v>2</v>
+        <v>408</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6538,12 +6534,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>19594091</t>
+          <t>1216515131</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19594091</t>
+          <t>https://m.place.naver.com/place/1216515131</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6555,38 +6551,34 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>검사,분석,조사</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>삼영검사엔지니어링</t>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>activism9090@naver.com</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>samyong@samyong.co.kr</t>
-        </is>
-      </c>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>032-888-8753</t>
+          <t>070-8075-9649</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 서구 백범로934번길 10-14</t>
+          <t>인천광역시 동구 송림동</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://www.samyong.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6596,7 +6588,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6636,12 +6628,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>35639490</t>
+          <t>1922639678</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35639490</t>
+          <t>https://m.place.naver.com/place/1922639678</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6653,39 +6645,39 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>피트니스 연구소 용현점 헬스 PT</t>
+          <t>조짐</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>lfitness3@naver.com</t>
+          <t>jo-gym@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1327-2357</t>
+          <t>032-777-9682</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 68 예승프라자 4층, 5층</t>
+          <t>인천광역시 동구 화수로 7 301호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.fitnessinstitute.co.kr/</t>
+          <t>https://blog.naver.com/jo-gym</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6706,22 +6698,22 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1728</v>
+        <v>42</v>
       </c>
       <c r="Q67" t="n">
-        <v>724</v>
+        <v>66</v>
       </c>
       <c r="R67" t="n">
-        <v>2452</v>
+        <v>108</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6730,12 +6722,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1279263313</t>
+          <t>1068496707</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1279263313</t>
+          <t>https://m.place.naver.com/place/1068496707</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6747,34 +6739,34 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>주택전시관</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1:1 개인PT샵 팻번</t>
+          <t>두산위브더센트럴도화</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>gbw21@naver.com</t>
+          <t>drive023@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>032-246-2158</t>
+          <t>070-8041-9638</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 서구 건지로 375 5층 팻번</t>
+          <t>인천광역시 미추홀구 숭의동</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gbw21</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6784,12 +6776,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6805,17 +6797,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>260</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>408</v>
+        <v>1</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6824,12 +6816,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1216515131</t>
+          <t>1980343684</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1216515131</t>
+          <t>https://m.place.naver.com/place/1980343684</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6841,30 +6833,34 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>하프짐휘트니스 배다리점</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>halfgym@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>070-8934-5659</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 24 6층</t>
+          <t>인천광역시 동구 만석동</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/halfgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6874,12 +6870,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6899,13 +6895,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>394</v>
+        <v>0</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6914,12 +6910,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1222280711</t>
+          <t>1837633354</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222280711</t>
+          <t>https://m.place.naver.com/place/1837633354</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6931,23 +6927,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>070-8935-6258</t>
+          <t>070-8039-8719</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -7008,12 +7004,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1439213164</t>
+          <t>1471027621</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1439213164</t>
+          <t>https://m.place.naver.com/place/1471027621</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7025,34 +7021,34 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>동익인간 원스텝짐_도화동 헬스장&amp;PT</t>
+          <t>포멀짐 헬스&amp;피티 제물포점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>godblessjiyu@naver.com</t>
+          <t>formalgym@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1420-5777</t>
+          <t>0507-1365-5941</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 19 영프라자3차 3층</t>
+          <t>인천광역시 미추홀구 경인로 128 2층 포멀짐</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/godblessjiyu</t>
+          <t>https://blog.naver.com/formalgym</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7090,10 +7086,10 @@
         <v>102</v>
       </c>
       <c r="Q71" t="n">
-        <v>351</v>
+        <v>9</v>
       </c>
       <c r="R71" t="n">
-        <v>453</v>
+        <v>111</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7102,12 +7098,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1374352371</t>
+          <t>1933593128</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1374352371</t>
+          <t>https://m.place.naver.com/place/1933593128</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7119,29 +7115,29 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>070-8940-8832</t>
+          <t>070-8039-9883</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 도화동</t>
+          <t>인천광역시 서구 가좌동</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7196,12 +7192,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1336050744</t>
+          <t>1018031898</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1336050744</t>
+          <t>https://m.place.naver.com/place/1018031898</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7213,25 +7209,29 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>기업</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>피티코리아</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>p-t-korea@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>070-8934-1302</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 서구 보도진로73번길 8</t>
+          <t>인천광역시 중구 신흥동1가</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>2142125524</t>
+          <t>1605821182</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2142125524</t>
+          <t>https://m.place.naver.com/place/1605821182</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7303,34 +7303,34 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>수학교육</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PT수학교습소</t>
+          <t>에이지트레이닝피티 주안점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>realyjkim@naver.com</t>
+          <t>ag_training@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1378-6566</t>
+          <t>0507-1305-5338</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로88번길 46 상가동 203호</t>
+          <t>인천광역시 미추홀구 경인로325번길 27 3층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ag_training</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7340,12 +7340,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7361,17 +7361,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7380,12 +7380,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1491165182</t>
+          <t>2007007809</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1491165182</t>
+          <t>https://m.place.naver.com/place/2007007809</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7413,13 +7413,13 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>070-8934-5659</t>
+          <t>070-8935-6258</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 동구 만석동</t>
+          <t>인천광역시 동구 송현동</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1837633354</t>
+          <t>1439213164</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1837633354</t>
+          <t>https://m.place.naver.com/place/1439213164</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">

--- a/naver-place-crawler/results_health/동구_PT.xlsx
+++ b/naver-place-crawler/results_health/동구_PT.xlsx
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>수학교육</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>온핏</t>
+          <t>PT수학교습소</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rlaqhqls3@naver.com</t>
+          <t>realyjkim@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1301-5868</t>
+          <t>0507-1378-6566</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 중구 제물량로166번길 1-27 4층</t>
+          <t>인천광역시 미추홀구 숙골로88번길 46 상가동 203호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlaqhqls3</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2071989754</t>
+          <t>1491165182</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2071989754</t>
+          <t>https://m.place.naver.com/place/1491165182</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>와이키키짐 PT 주안점</t>
+          <t>넘버제로짐 헬스&amp;PT 주안역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>waikikigym2311@naver.com</t>
+          <t>sid1287@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1365-4408</t>
+          <t>0507-1363-2606</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 710 지하1층</t>
+          <t>인천광역시 미추홀구 미추홀대로 725 5층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/waikikigym_jwsong?igsh=bG51c2U5anlmZ2Ez&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/no.0pt/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>121</v>
+        <v>334</v>
       </c>
       <c r="Q3" t="n">
-        <v>1533</v>
+        <v>515</v>
       </c>
       <c r="R3" t="n">
-        <v>1654</v>
+        <v>849</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1085067011</t>
+          <t>1326633826</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1085067011</t>
+          <t>https://m.place.naver.com/place/1326633826</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에이셉 트레이닝 센터</t>
+          <t>1:1 개인PT샵 팻번</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>asap_hs@naver.com</t>
+          <t>gbw21@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1364-4608</t>
+          <t>032-246-2158</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 중구 개항로 69 3층</t>
+          <t>인천광역시 서구 건지로 375 5층 팻번</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/swwTRafc</t>
+          <t>https://blog.naver.com/gbw21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>39</v>
+        <v>148</v>
       </c>
       <c r="Q4" t="n">
-        <v>153</v>
+        <v>260</v>
       </c>
       <c r="R4" t="n">
-        <v>192</v>
+        <v>408</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +824,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1192923099</t>
+          <t>1216515131</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192923099</t>
+          <t>https://m.place.naver.com/place/1216515131</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>여성전용 헬스 PT 바른습관PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>eventheo@naver.com</t>
+          <t>hyptjuan@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>070-8039-8722</t>
+          <t>0507-1466-0535</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수1.화평동</t>
+          <t>인천광역시 미추홀구 염창로 65 여성전용 헬스 PT 바른습관PT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mgm_hypt?igsh=ODA1NTc5OTg5Nw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -899,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +918,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1705374816</t>
+          <t>1761795724</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1705374816</t>
+          <t>https://m.place.naver.com/place/1761795724</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>워라블짐 헬스 PT 도화점</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>wlb1203@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1405-1273</t>
+          <t>070-8940-8832</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 251 3층 워라블짐</t>
+          <t>인천광역시 미추홀구 도화동</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wlb1203</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1012,47 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1596200279</t>
+          <t>1336050744</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596200279</t>
+          <t>https://m.place.naver.com/place/1336050744</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>동익인간 원스텝짐_도화동 헬스장&amp;PT</t>
+          <t>몬스터PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>godblessjiyu@naver.com</t>
+          <t>dankkh418@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1420-5777</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 19 영프라자3차 3층</t>
+          <t>인천광역시 동구 송림로43번길 29 (송림동) 몬스터PT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/godblessjiyu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,12 +1062,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1087,17 +1083,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="Q7" t="n">
-        <v>351</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>453</v>
+        <v>25</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1102,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1374352371</t>
+          <t>1931268009</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1374352371</t>
+          <t>https://m.place.naver.com/place/1931268009</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>거뜬하다</t>
+          <t>서인짐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gongju1432@naver.com</t>
+          <t>rlatjdls0305@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1371-4266</t>
+          <t>0507-1384-9886</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 북항로32번안길 36 청라M골프 2층 헬스장</t>
+          <t>인천광역시 미추홀구 경인로 133 2층 서인짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/rlatjdls0305</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,12 +1156,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="R8" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1196,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1742455296</t>
+          <t>1817968809</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742455296</t>
+          <t>https://m.place.naver.com/place/1817968809</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>라이프 P.T</t>
+          <t>온힘PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mkj1104@naver.com</t>
+          <t>onhim4477@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1366-6002</t>
+          <t>0507-1441-4477</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 221 101동 214호</t>
+          <t>인천광역시 동구 송현로 33 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/onhim4477</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,12 +1250,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,17 +1271,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,66 +1290,66 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2087474006</t>
+          <t>2064548442</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087474006</t>
+          <t>https://m.place.naver.com/place/2064548442</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>피트니스 연구소 용현점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>lfitness3@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>070-8931-8100</t>
+          <t>0507-1327-2357</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가좌동</t>
+          <t>인천광역시 미추홀구 인주대로 68 예승프라자 4층, 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1364,22 +1360,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1728</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>727</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2455</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1857339040</t>
+          <t>1279263313</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1857339040</t>
+          <t>https://m.place.naver.com/place/1279263313</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT 주안점</t>
+          <t>모두짐 재활PT 인천도화점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tpg21@naver.com</t>
+          <t>modoo2206@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1360-9997</t>
+          <t>0507-1484-5789</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 730 고려빌딩 4층</t>
+          <t>인천광역시 미추홀구 숙골로87번길 28-1 다온1프라자 5층 모두짐 인천도화점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tpgymjooan.com/</t>
+          <t>https://youtube.com/@mutongweight</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1458,7 +1454,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1467,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1150</v>
+        <v>238</v>
       </c>
       <c r="Q11" t="n">
-        <v>1397</v>
+        <v>323</v>
       </c>
       <c r="R11" t="n">
-        <v>2547</v>
+        <v>561</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1015443504</t>
+          <t>1514606541</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1015443504</t>
+          <t>https://m.place.naver.com/place/1514606541</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1504,34 +1500,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>넘버제로짐 헬스&amp;PT 주안역점</t>
+          <t>인싸짐 가좌점 24시연중무휴 PT 헬스장</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sid1287@naver.com</t>
+          <t>wjdguss1045@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1363-2606</t>
+          <t>0507-1376-3818</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 725 5층</t>
+          <t>인천광역시 서구 원적로 100 지하2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/no.0pt/</t>
+          <t>http://pf.kakao.com/_SxiUZG</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1552,7 +1548,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1561,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>333</v>
+        <v>1189</v>
       </c>
       <c r="Q12" t="n">
-        <v>515</v>
+        <v>748</v>
       </c>
       <c r="R12" t="n">
-        <v>848</v>
+        <v>1937</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,51 +1572,51 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1326633826</t>
+          <t>1748758798</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1326633826</t>
+          <t>https://m.place.naver.com/place/1748758798</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT 가좌점</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>turningpointgym_gajw@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>032-576-1365</t>
+          <t>070-8935-6258</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 85 우신프라자 B1층 B01~B02호</t>
+          <t>인천광역시 동구 송현동</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/turningpointgym_gajw</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1630,12 +1626,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1651,17 +1647,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>538</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1549</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2087</v>
+        <v>0</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1588426455</t>
+          <t>1439213164</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1588426455</t>
+          <t>https://m.place.naver.com/place/1439213164</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1692,34 +1688,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>인싸짐 가좌점 24시연중무휴 PT 헬스장</t>
+          <t>바디피티&amp;스킨뷰티</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>wjdguss1045@naver.com</t>
+          <t>ydh5645sd@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1376-3818</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 100 지하2층</t>
+          <t>인천광역시 동구 수문통로 29 3층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_SxiUZG</t>
+          <t>https://blog.naver.com/ydh5645sd</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1729,7 +1721,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1740,7 +1732,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1749,13 +1741,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1189</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>748</v>
+        <v>20</v>
       </c>
       <c r="R14" t="n">
-        <v>1937</v>
+        <v>24</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,17 +1756,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1748758798</t>
+          <t>13137004</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1748758798</t>
+          <t>https://m.place.naver.com/place/13137004</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1786,29 +1778,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>유코치의슬림해짐</t>
+          <t>글로리트레이닝센터</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>syhs007@naver.com</t>
+          <t>seung1105-@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1465-4459</t>
+          <t>0507-1418-4930</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 제일로 31 상가 2층 205호</t>
+          <t>인천광역시 서구 북항로32번안길 8 506호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yoocoach007</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1818,7 +1810,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1839,17 +1831,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,51 +1850,51 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1250104868</t>
+          <t>2015431625</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1250104868</t>
+          <t>https://m.place.naver.com/place/2015431625</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>진스 핏</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>jeansfit@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>070-8935-9039</t>
+          <t>0507-1399-8039</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안동</t>
+          <t>인천광역시 미추홀구 경인로 84 4층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jeans_fit77?igsh=cXg0ZTZ0N203emlt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1912,7 +1904,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1933,17 +1925,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,51 +1944,47 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1998758780</t>
+          <t>2036358510</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1998758780</t>
+          <t>https://m.place.naver.com/place/2036358510</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>수디아필라테스프리미엄 2호점</t>
+          <t>하프짐휘트니스 배다리점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sudiayogapilates@naver.com</t>
+          <t>halfgym@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1319-9682</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 24 상가 B동 2층 208호</t>
+          <t>인천광역시 동구 송림로 24 6층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sudiayogapilates</t>
+          <t>https://blog.naver.com/halfgym</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2027,17 +2015,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>23</v>
+        <v>343</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="R17" t="n">
-        <v>38</v>
+        <v>394</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,17 +2034,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1626857525</t>
+          <t>1222280711</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626857525</t>
+          <t>https://m.place.naver.com/place/1222280711</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2056,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>루트짐 주안점</t>
+          <t>조짐</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rlawnsgh3347@naver.com</t>
+          <t>jo-gym@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1492-1172</t>
+          <t>032-777-9682</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로375번길 11 2층 루트짐 주안점</t>
+          <t>인천광역시 동구 화수로 7 301호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlawnsgh3347</t>
+          <t>https://blog.naver.com/jo-gym</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2116,22 +2104,22 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q18" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="R18" t="n">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2140,51 +2128,47 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1765729791</t>
+          <t>1068496707</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1765729791</t>
+          <t>https://m.place.naver.com/place/1068496707</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>진스 핏</t>
+          <t>CBBM휘트니스센타</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jeansfit@naver.com</t>
+          <t>csys026@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1399-8039</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 84 4층</t>
+          <t>인천광역시 미추홀구 독정이로 40 4층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jeans_fit77?igsh=cXg0ZTZ0N203emlt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2194,7 +2178,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2215,17 +2199,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2234,47 +2218,51 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2036358510</t>
+          <t>1707568333</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036358510</t>
+          <t>https://m.place.naver.com/place/1707568333</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>하프짐휘트니스 배다리점</t>
+          <t>온핏</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>halfgym@naver.com</t>
+          <t>rlaqhqls3@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1301-5868</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 24 6층</t>
+          <t>인천광역시 중구 제물량로166번길 1-27 4층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/halfgym</t>
+          <t>https://blog.naver.com/rlaqhqls3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2305,17 +2293,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>343</v>
+        <v>9</v>
       </c>
       <c r="Q20" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="R20" t="n">
-        <v>394</v>
+        <v>39</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,51 +2312,51 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1222280711</t>
+          <t>2071989754</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222280711</t>
+          <t>https://m.place.naver.com/place/2071989754</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>실내체육관</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>W GYM</t>
+          <t>가좌동헬스장PT 니드트레이닝센터</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mwgym2022@naver.com</t>
+          <t>ntc_2017@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>032-777-7749</t>
+          <t>0507-1408-8318</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 138 미지빌딩 3층</t>
+          <t>인천광역시 서구 원적로 78 3층 303호니드트레이닝센터 (ntc2017)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://cafe.naver.com/7777749</t>
+          <t>https://www.instagram.com/ntc2017_obs</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2383,7 +2371,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2399,17 +2387,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>323</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>373</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,51 +2406,51 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>19594091</t>
+          <t>40729664</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19594091</t>
+          <t>https://m.place.naver.com/place/40729664</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>더블유닛</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>unit4579@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1370-4579</t>
+          <t>070-8039-9870</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로 82-1 4층~5층 더블유닛</t>
+          <t>인천광역시 미추홀구 숭의동</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unit4579</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2472,12 +2460,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2493,17 +2481,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>741</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>798</v>
+        <v>0</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2512,66 +2500,66 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1895113732</t>
+          <t>1205878365</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895113732</t>
+          <t>https://m.place.naver.com/place/1205878365</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>카우짐 송림점</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dongdo0033@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1454-7938</t>
+          <t>070-8934-5659</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 80 303호</t>
+          <t>인천광역시 동구 만석동</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/dw9626</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2587,17 +2575,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>457</v>
+        <v>0</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2606,46 +2594,46 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1970713518</t>
+          <t>1837633354</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1970713518</t>
+          <t>https://m.place.naver.com/place/1837633354</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>rodtmdu12@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>070-8088-7806</t>
+          <t>070-8039-8720</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수1.화평동</t>
+          <t>인천광역시 동구 창영동</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2700,51 +2688,51 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1421179794</t>
+          <t>1037835069</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421179794</t>
+          <t>https://m.place.naver.com/place/1037835069</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>웨이빗 피트니스 24시 헬스 PT 주안점</t>
+          <t>피티아시바</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>weibit@naver.com</t>
+          <t>unixgaseol7@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1328-8048</t>
+          <t>070-5255-2586</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 716 6층 웨이빗 피트니스</t>
+          <t>인천광역시 동구 화수1.화평동</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/weibit_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2754,7 +2742,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2775,17 +2763,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2917</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>782</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3699</v>
+        <v>0</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2794,17 +2782,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1700131075</t>
+          <t>1111897979</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1700131075</t>
+          <t>https://m.place.naver.com/place/1111897979</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2816,39 +2804,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>글로리트레이닝센터</t>
+          <t>에이셉 트레이닝 센터</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>seung1105-@naver.com</t>
+          <t>asap_hs@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1418-4930</t>
+          <t>0507-1364-4608</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 서구 북항로32번안길 8 506호</t>
+          <t>인천광역시 중구 개항로 69 3층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/swwTRafc</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2864,22 +2852,22 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>153</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>192</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2888,51 +2876,51 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2015431625</t>
+          <t>1192923099</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015431625</t>
+          <t>https://m.place.naver.com/place/1192923099</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>워라블짐 헬스 PT 도화점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>wlb1203@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>070-8940-8832</t>
+          <t>0507-1405-1273</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 도화동</t>
+          <t>인천광역시 미추홀구 경인로 251 3층 워라블짐</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wlb1203</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2942,12 +2930,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2963,17 +2951,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2982,51 +2970,51 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1336050744</t>
+          <t>1596200279</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1336050744</t>
+          <t>https://m.place.naver.com/place/1596200279</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>케이짐 인천도화점</t>
+          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>la4200@naver.com</t>
+          <t>rodtmdu12@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1459-0283</t>
+          <t>070-8040-5383</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 59 3층</t>
+          <t>인천광역시 미추홀구 주안동</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/la4200</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3036,12 +3024,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3057,17 +3045,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3076,51 +3064,51 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1115746281</t>
+          <t>1889265333</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1115746281</t>
+          <t>https://m.place.naver.com/place/1889265333</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>어테인휘트니스 헬스&amp;PT 석남점</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>attain_fitness@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1337-3765</t>
+          <t>070-8039-9883</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 서구 길주로 101-1 투썸플레이스건물 4층</t>
+          <t>인천광역시 서구 가좌동</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/attain.fitness1/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3130,7 +3118,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3146,22 +3134,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>355</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>875</v>
+        <v>0</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3170,46 +3158,46 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1639913680</t>
+          <t>1018031898</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1639913680</t>
+          <t>https://m.place.naver.com/place/1018031898</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>eventheo@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>070-8039-9870</t>
+          <t>070-8931-8100</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숭의동</t>
+          <t>인천광역시 서구 가좌동</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3264,46 +3252,46 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1205878365</t>
+          <t>1857339040</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1205878365</t>
+          <t>https://m.place.naver.com/place/1857339040</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>수학교육</t>
+          <t>전문건설업</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PT수학교습소</t>
+          <t>비티아시바피티아시바이동식비계가설재판매임대설치</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>realyjkim@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1378-6566</t>
+          <t>070-8055-2249</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로88번길 46 상가동 203호</t>
+          <t>인천광역시 동구 창영동</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3358,46 +3346,46 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1491165182</t>
+          <t>1664508720</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1491165182</t>
+          <t>https://m.place.naver.com/place/1664508720</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>070-8082-0818</t>
+          <t>070-8932-2324</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 동구 만석동</t>
+          <t>인천광역시 동구 화수동</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3437,13 +3425,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3452,51 +3440,51 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1744427872</t>
+          <t>1708292189</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1744427872</t>
+          <t>https://m.place.naver.com/place/1708292189</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>모두짐 재활PT 인천도화점</t>
+          <t>동익인간 원스텝짐_도화동 헬스장&amp;PT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>modoo2206@naver.com</t>
+          <t>godblessjiyu@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1484-5789</t>
+          <t>0507-1420-5777</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 28-1 다온1프라자 5층 모두짐 인천도화점</t>
+          <t>인천광역시 미추홀구 숙골로95번길 19 영프라자3차 3층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://youtube.com/@mutongweight</t>
+          <t>https://blog.naver.com/godblessjiyu</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3511,7 +3499,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3531,13 +3519,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>238</v>
+        <v>102</v>
       </c>
       <c r="Q33" t="n">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="R33" t="n">
-        <v>561</v>
+        <v>453</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3546,42 +3534,46 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1514606541</t>
+          <t>1374352371</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1514606541</t>
+          <t>https://m.place.naver.com/place/1374352371</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>몬스터PT</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dankkh418@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>070-8940-6264</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로43번길 29 (송림동) 몬스터PT</t>
+          <t>인천광역시 동구 송림동</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3621,13 +3613,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3636,51 +3628,51 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1931268009</t>
+          <t>1088618869</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1931268009</t>
+          <t>https://m.place.naver.com/place/1088618869</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>여성전용 헬스 PT 바른습관PT</t>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>hyptjuan@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1466-0535</t>
+          <t>070-8075-9649</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염창로 65 여성전용 헬스 PT 바른습관PT</t>
+          <t>인천광역시 동구 송림동</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mgm_hypt?igsh=ODA1NTc5OTg5Nw%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3690,7 +3682,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3711,17 +3703,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3730,47 +3722,51 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1761795724</t>
+          <t>1922639678</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1761795724</t>
+          <t>https://m.place.naver.com/place/1922639678</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>페인트</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>피티상사</t>
+          <t>더블유닛</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>partnersdh@naver.com</t>
+          <t>unit4579@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1370-4579</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로 136-1 1층</t>
+          <t>인천광역시 중구 우현로 82-1 4층~5층 더블유닛</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/unit4579</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3780,12 +3776,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3801,17 +3797,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>741</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>798</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3820,51 +3816,51 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2034784321</t>
+          <t>1895113732</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2034784321</t>
+          <t>https://m.place.naver.com/place/1895113732</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>바디에이프PT&amp;헬스 주안점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>apecompany@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>070-8935-8172</t>
+          <t>0507-1321-5947</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숭의동</t>
+          <t>인천광역시 미추홀구 석정로 430 3층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/apecompany</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3874,12 +3870,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3895,17 +3891,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>406</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3914,56 +3910,56 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1359470432</t>
+          <t>1479770189</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1359470432</t>
+          <t>https://m.place.naver.com/place/1479770189</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>피트니스 연구소 용현점 헬스 PT</t>
+          <t>수디아요가필라테스 동인천</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>lfitness3@naver.com</t>
+          <t>sudiayogapilates@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1327-2357</t>
+          <t>0507-1396-9683</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 68 예승프라자 4층, 5층</t>
+          <t>인천광역시 동구 송현로 30 4층 수디아 요가필라테스 동인천</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.fitnessinstitute.co.kr/</t>
+          <t>https://blog.naver.com/sudiayogapilates</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3984,7 +3980,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3993,13 +3989,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1728</v>
+        <v>531</v>
       </c>
       <c r="Q38" t="n">
-        <v>726</v>
+        <v>209</v>
       </c>
       <c r="R38" t="n">
-        <v>2454</v>
+        <v>740</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,51 +4004,51 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1279263313</t>
+          <t>1388556375</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1279263313</t>
+          <t>https://m.place.naver.com/place/1388556375</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>터닝포인트짐 헬스 PT 가좌점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>eventheo@naver.com</t>
+          <t>turningpointgym_gajw@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>070-8039-8721</t>
+          <t>032-576-1365</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수동</t>
+          <t>인천광역시 서구 원적로 85 우신프라자 B1층 B01~B02호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/turningpointgym_gajw</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4062,12 +4058,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4083,17 +4079,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1549</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2087</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,51 +4098,47 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1832168408</t>
+          <t>1588426455</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1832168408</t>
+          <t>https://m.place.naver.com/place/1588426455</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>올타임클래식짐 헬스PT 주안도화점</t>
+          <t>국가대표 박인정 PT샵 주안본점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>all_time_classic@naver.com</t>
+          <t>powerman962@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0507-1372-9682</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로 604 롯데월드타워오피스텔 B1층</t>
+          <t>인천광역시 미추홀구 경인로325번길 27 미추홀더리브아파트 상가 2F</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/alltimeclassic_gym?igsh=cWV5d3BqdXF2MHI4&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/pij_pt_shop</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4181,13 +4173,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>221</v>
+        <v>95</v>
       </c>
       <c r="Q40" t="n">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="R40" t="n">
-        <v>322</v>
+        <v>136</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,42 +4188,46 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2001570240</t>
+          <t>1611506975</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001570240</t>
+          <t>https://m.place.naver.com/place/1611506975</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>기업</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>피티코리아</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>p-t-korea@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>070-8935-9039</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 서구 보도진로73번길 8</t>
+          <t>인천광역시 미추홀구 주안동</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4286,51 +4282,51 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2142125524</t>
+          <t>1998758780</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2142125524</t>
+          <t>https://m.place.naver.com/place/1998758780</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>서인짐</t>
+          <t>에이지트레이닝피티 주안점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>rlatjdls0305@naver.com</t>
+          <t>ag_training@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1384-9886</t>
+          <t>0507-1305-5338</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 133 2층 서인짐</t>
+          <t>인천광역시 미추홀구 경인로325번길 27 3층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlatjdls0305</t>
+          <t>https://blog.naver.com/ag_training</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4361,17 +4357,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q42" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4380,17 +4376,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1817968809</t>
+          <t>2007007809</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817968809</t>
+          <t>https://m.place.naver.com/place/2007007809</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4402,29 +4398,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>가좌동헬스장PT 니드트레이닝센터</t>
+          <t>케이짐 인천도화점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ntc_2017@naver.com</t>
+          <t>la4200@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1408-8318</t>
+          <t>0507-1459-0283</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 78 3층 303호니드트레이닝센터 (ntc2017)</t>
+          <t>인천광역시 미추홀구 염전로202번길 59 3층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ntc2017_obs</t>
+          <t>https://blog.naver.com/la4200</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4439,7 +4435,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4459,13 +4455,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="Q43" t="n">
-        <v>323</v>
+        <v>43</v>
       </c>
       <c r="R43" t="n">
-        <v>373</v>
+        <v>66</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4474,51 +4470,51 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>40729664</t>
+          <t>1115746281</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/40729664</t>
+          <t>https://m.place.naver.com/place/1115746281</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
+          <t>와이키키짐 PT 주안점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>rodtmdu12@naver.com</t>
+          <t>waikikigym2311@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>070-8040-5383</t>
+          <t>0507-1365-4408</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안동</t>
+          <t>인천광역시 미추홀구 미추홀대로 710 지하1층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/waikikigym_jwsong?igsh=bG51c2U5anlmZ2Ez&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4528,7 +4524,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4549,17 +4545,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1533</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1654</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4568,17 +4564,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1889265333</t>
+          <t>1085067011</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1889265333</t>
+          <t>https://m.place.naver.com/place/1085067011</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4586,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4601,13 +4597,13 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>070-8009-0489</t>
+          <t>070-8039-8722</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 중구 선화동</t>
+          <t>인천광역시 동구 화수1.화평동</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4662,17 +4658,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1430700696</t>
+          <t>1705374816</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430700696</t>
+          <t>https://m.place.naver.com/place/1705374816</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4684,29 +4680,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>온힘PT</t>
+          <t>거뜬하다</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>onhim4477@naver.com</t>
+          <t>gongju1432@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1441-4477</t>
+          <t>0507-1371-4266</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 33 3층</t>
+          <t>인천광역시 서구 북항로32번안길 36 청라M골프 2층 헬스장</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/onhim4477</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4716,12 +4712,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4737,17 +4733,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Q46" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4756,47 +4752,51 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2064548442</t>
+          <t>1742455296</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064548442</t>
+          <t>https://m.place.naver.com/place/1742455296</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>바디피티&amp;스킨뷰티</t>
+          <t>포멀짐 헬스&amp;피티 제물포점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ydh5645sd@naver.com</t>
+          <t>formalgym@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1365-5941</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 동구 수문통로 29 3층</t>
+          <t>인천광역시 미추홀구 경인로 128 2층 포멀짐</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ydh5645sd</t>
+          <t>https://blog.naver.com/formalgym</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="Q47" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="R47" t="n">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4846,17 +4846,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>13137004</t>
+          <t>1933593128</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13137004</t>
+          <t>https://m.place.naver.com/place/1933593128</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4868,24 +4868,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>피티아시바</t>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>unixgaseol7@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>070-5255-2586</t>
+          <t>070-8068-4960</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수1.화평동</t>
+          <t>인천광역시 동구 송현동</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4940,17 +4940,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1111897979</t>
+          <t>1006757127</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1111897979</t>
+          <t>https://m.place.naver.com/place/1006757127</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4962,25 +4962,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>국가대표 박인정 PT샵 주안본점</t>
+          <t>도모 스트렝스</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>powerman962@naver.com</t>
+          <t>5tokoda@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1334-7275</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로325번길 27 미추홀더리브아파트 상가 2F</t>
+          <t>인천광역시 미추홀구 석정로 244 지하1층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pij_pt_shop</t>
+          <t>https://youtube.com/@Domo_otokoda?si=vWR7lJmjGYe0J-VO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5015,13 +5019,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="Q49" t="n">
-        <v>41</v>
+        <v>273</v>
       </c>
       <c r="R49" t="n">
-        <v>136</v>
+        <v>320</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5030,17 +5034,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1611506975</t>
+          <t>1628768408</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611506975</t>
+          <t>https://m.place.naver.com/place/1628768408</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5134,41 +5138,37 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>페인트</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>쎈 PT 스튜디오 인천도화점</t>
+          <t>피티상사</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ssenptstudio@naver.com</t>
+          <t>partnersdh@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0507-1362-0833</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 2 센타프라자 203호</t>
+          <t>인천광역시 동구 샛골로 136-1 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssenptstudio</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5194,22 +5194,22 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>281</v>
+        <v>1</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5218,51 +5218,51 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1691655395</t>
+          <t>2034784321</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1691655395</t>
+          <t>https://m.place.naver.com/place/2034784321</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JD휘트니스짐</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>balakas0101@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1408-9011</t>
+          <t>070-8039-8719</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 중구 신포로27번길 3</t>
+          <t>인천광역시 동구 송현동</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/balakas0101</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5312,61 +5312,61 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>16341034</t>
+          <t>1471027621</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16341034</t>
+          <t>https://m.place.naver.com/place/1471027621</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>피티아시바</t>
+          <t>터닝포인트짐 헬스 PT 주안점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unixgaseol7@naver.com</t>
+          <t>tpg21@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>070-5255-5213</t>
+          <t>0507-1360-9997</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림동</t>
+          <t>인천광역시 미추홀구 미추홀대로 730 고려빌딩 4층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.tpgymjooan.com/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5382,22 +5382,22 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1150</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>1397</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2547</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5406,17 +5406,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1799811597</t>
+          <t>1015443504</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1799811597</t>
+          <t>https://m.place.naver.com/place/1015443504</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5428,24 +5428,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>피티아시바</t>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>unixgaseol7@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>070-5255-9064</t>
+          <t>070-8082-0818</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가좌동</t>
+          <t>인천광역시 동구 만석동</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5485,13 +5485,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5500,17 +5500,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1127060177</t>
+          <t>1744427872</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1127060177</t>
+          <t>https://m.place.naver.com/place/1744427872</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5522,29 +5522,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>도모 스트렝스</t>
+          <t>쎈 PT 스튜디오 인천도화점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>5tokoda@naver.com</t>
+          <t>ssenptstudio@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1334-7275</t>
+          <t>0507-1362-0833</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로 244 지하1층</t>
+          <t>인천광역시 미추홀구 숙골로87번길 2 센타프라자 203호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://youtube.com/@Domo_otokoda?si=vWR7lJmjGYe0J-VO</t>
+          <t>https://blog.naver.com/ssenptstudio</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5570,7 +5570,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5579,13 +5579,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>47</v>
+        <v>229</v>
       </c>
       <c r="Q55" t="n">
-        <v>273</v>
+        <v>52</v>
       </c>
       <c r="R55" t="n">
-        <v>320</v>
+        <v>281</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5594,51 +5594,51 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1628768408</t>
+          <t>1691655395</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628768408</t>
+          <t>https://m.place.naver.com/place/1691655395</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>수디아필라테스프리미엄 2호점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>sudiayogapilates@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>070-8940-6264</t>
+          <t>0507-1319-9682</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림동</t>
+          <t>인천광역시 동구 송현로 24 상가 B동 2층 208호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sudiayogapilates</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5669,17 +5669,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5688,62 +5688,66 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1088618869</t>
+          <t>1626857525</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088618869</t>
+          <t>https://m.place.naver.com/place/1626857525</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CBBM휘트니스센타</t>
+          <t>카우짐 송림점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>csys026@naver.com</t>
+          <t>dongdo0033@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1454-7938</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독정이로 40 4층</t>
+          <t>인천광역시 동구 송림로 80 303호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://link.inpock.co.kr/dw9626</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5759,17 +5763,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q57" t="n">
-        <v>2</v>
+        <v>157</v>
       </c>
       <c r="R57" t="n">
-        <v>2</v>
+        <v>457</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5778,46 +5782,46 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1707568333</t>
+          <t>1970713518</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1707568333</t>
+          <t>https://m.place.naver.com/place/1970713518</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>라이프 P.T</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>eventheo@naver.com</t>
+          <t>mkj1104@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>070-8039-8720</t>
+          <t>0507-1366-6002</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 동구 창영동</t>
+          <t>인천광역시 미추홀구 경인로 221 101동 214호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5872,40 +5876,40 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1037835069</t>
+          <t>2087474006</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037835069</t>
+          <t>https://m.place.naver.com/place/2087474006</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>070-8932-2324</t>
+          <t>070-8039-8721</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -5966,51 +5970,51 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1708292189</t>
+          <t>1832168408</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1708292189</t>
+          <t>https://m.place.naver.com/place/1832168408</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>루트짐 주안점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>rlawnsgh3347@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>070-8935-9112</t>
+          <t>0507-1492-1172</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 중구 도원동</t>
+          <t>인천광역시 미추홀구 석정로375번길 11 2층 루트짐 주안점</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/rlawnsgh3347</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6020,12 +6024,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6036,22 +6040,22 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="R60" t="n">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6060,17 +6064,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1889289229</t>
+          <t>1765729791</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1889289229</t>
+          <t>https://m.place.naver.com/place/1765729791</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6082,24 +6086,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+          <t>피티아시바</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>unixgaseol7@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>070-8068-4960</t>
+          <t>070-5255-9064</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현동</t>
+          <t>인천광역시 서구 가좌동</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6154,46 +6158,46 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1006757127</t>
+          <t>1127060177</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1006757127</t>
+          <t>https://m.place.naver.com/place/1127060177</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>전문건설업</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>비티아시바피티아시바이동식비계가설재판매임대설치</t>
+          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>rodtmdu12@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>070-8055-2249</t>
+          <t>070-8088-7806</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 동구 창영동</t>
+          <t>인천광역시 동구 화수1.화평동</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6248,55 +6252,51 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1664508720</t>
+          <t>1421179794</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1664508720</t>
+          <t>https://m.place.naver.com/place/1421179794</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>검사,분석,조사</t>
+          <t>주택전시관</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>삼영검사엔지니어링</t>
+          <t>두산위브더센트럴도화</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>activism9090@naver.com</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>samyong@samyong.co.kr</t>
-        </is>
-      </c>
+          <t>genie_sim@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>032-888-8753</t>
+          <t>070-8041-9638</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 서구 백범로934번길 10-14</t>
+          <t>인천광역시 미추홀구 숭의동</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://www.samyong.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6334,10 +6334,10 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6346,51 +6346,51 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>35639490</t>
+          <t>1980343684</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35639490</t>
+          <t>https://m.place.naver.com/place/1980343684</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>수디아요가필라테스 동인천</t>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sudiayogapilates@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1396-9683</t>
+          <t>070-8009-0489</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 30 4층 수디아 요가필라테스 동인천</t>
+          <t>인천광역시 중구 선화동</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sudiayogapilates</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6421,17 +6421,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>740</v>
+        <v>0</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6440,51 +6440,51 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1388556375</t>
+          <t>1430700696</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1388556375</t>
+          <t>https://m.place.naver.com/place/1430700696</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1:1 개인PT샵 팻번</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>gbw21@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>032-246-2158</t>
+          <t>070-8935-9112</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 서구 건지로 375 5층 팻번</t>
+          <t>인천광역시 중구 도원동</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gbw21</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6515,17 +6515,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>408</v>
+        <v>1</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6534,51 +6534,51 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1216515131</t>
+          <t>1889289229</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1216515131</t>
+          <t>https://m.place.naver.com/place/1889289229</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+          <t>어테인휘트니스 헬스&amp;PT 석남점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>attain_fitness@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>070-8075-9649</t>
+          <t>0507-1337-3765</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림동</t>
+          <t>인천광역시 서구 길주로 101-1 투썸플레이스건물 4층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/attain.fitness1/</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6604,22 +6604,22 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6628,51 +6628,51 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1922639678</t>
+          <t>1639913680</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1922639678</t>
+          <t>https://m.place.naver.com/place/1639913680</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>조짐</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>jo-gym@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>032-777-9682</t>
+          <t>070-8935-8172</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수로 7 301호</t>
+          <t>인천광역시 미추홀구 숭의동</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jo-gym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6707,13 +6707,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6722,51 +6722,51 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1068496707</t>
+          <t>1359470432</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1068496707</t>
+          <t>https://m.place.naver.com/place/1359470432</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>주택전시관</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>두산위브더센트럴도화</t>
+          <t>유코치의슬림해짐</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>drive023@naver.com</t>
+          <t>syhs007@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>070-8041-9638</t>
+          <t>0507-1465-4459</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숭의동</t>
+          <t>인천광역시 미추홀구 제일로 31 상가 2층 205호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/yoocoach007</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6797,17 +6797,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="R68" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6816,51 +6816,51 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1980343684</t>
+          <t>1250104868</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1980343684</t>
+          <t>https://m.place.naver.com/place/1250104868</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>올타임클래식짐 헬스PT 주안도화점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>all_time_classic@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>070-8934-5659</t>
+          <t>0507-1372-9682</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 동구 만석동</t>
+          <t>인천광역시 미추홀구 한나루로 604 롯데월드타워오피스텔 B1층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/alltimeclassic_gym?igsh=cWV5d3BqdXF2MHI4&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6891,17 +6891,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6910,46 +6910,46 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1837633354</t>
+          <t>2001570240</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1837633354</t>
+          <t>https://m.place.naver.com/place/2001570240</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>웅변,화술</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>eventheo@naver.com</t>
+          <t>jcomz7@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>070-8039-8719</t>
+          <t>070-8934-1302</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현동</t>
+          <t>인천광역시 중구 신흥동1가</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7004,56 +7004,60 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1471027621</t>
+          <t>1605821182</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471027621</t>
+          <t>https://m.place.naver.com/place/1605821182</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>검사,분석,조사</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>포멀짐 헬스&amp;피티 제물포점</t>
+          <t>삼영검사엔지니어링</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>formalgym@naver.com</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>activism9090@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>samyong@samyong.co.kr</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1365-5941</t>
+          <t>032-888-8753</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 128 2층 포멀짐</t>
+          <t>인천광역시 서구 백범로934번길 10-14</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/formalgym</t>
+          <t>http://www.samyong.co.kr/</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7063,7 +7067,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7079,17 +7083,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7098,51 +7102,51 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1933593128</t>
+          <t>35639490</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1933593128</t>
+          <t>https://m.place.naver.com/place/35639490</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>웨이빗 피트니스 24시 헬스 PT 주안점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>eventheo@naver.com</t>
+          <t>weibit@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>070-8039-9883</t>
+          <t>0507-1328-8048</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가좌동</t>
+          <t>인천광역시 미추홀구 미추홀대로 716 6층 웨이빗 피트니스</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/weibit_official</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7152,7 +7156,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7173,17 +7177,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2917</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>783</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7192,46 +7196,42 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1018031898</t>
+          <t>1700131075</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1018031898</t>
+          <t>https://m.place.naver.com/place/1700131075</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>기업</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>피티코리아</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>p-t-korea@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>070-8934-1302</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 중구 신흥동1가</t>
+          <t>인천광역시 서구 보도진로73번길 8</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7286,56 +7286,56 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1605821182</t>
+          <t>2142125524</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1605821182</t>
+          <t>https://m.place.naver.com/place/2142125524</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>실내체육관</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>에이지트레이닝피티 주안점</t>
+          <t>W GYM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ag_training@naver.com</t>
+          <t>mwgym2022@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1305-5338</t>
+          <t>032-777-7749</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로325번길 27 3층</t>
+          <t>인천광역시 동구 송림로 138 미지빌딩 3층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ag_training</t>
+          <t>http://cafe.naver.com/7777749</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7361,18 +7361,18 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q74" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" t="n">
         <v>2</v>
       </c>
-      <c r="R74" t="n">
-        <v>6</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>X</t>
@@ -7380,46 +7380,46 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>2007007809</t>
+          <t>19594091</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007007809</t>
+          <t>https://m.place.naver.com/place/19594091</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>웅변,화술</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>뿌리스피치학원.리더십.시낭송모집.발표.PT.면접자기소개</t>
+          <t>피티아시바</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jcomz7@naver.com</t>
+          <t>unixgaseol7@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>070-8935-6258</t>
+          <t>070-5255-5213</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현동</t>
+          <t>인천광역시 동구 송림동</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7474,17 +7474,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1439213164</t>
+          <t>1799811597</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1439213164</t>
+          <t>https://m.place.naver.com/place/1799811597</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7496,29 +7496,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>바디에이프PT&amp;헬스 주안점</t>
+          <t>JD휘트니스짐</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>apecompany@naver.com</t>
+          <t>balakas0101@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1321-5947</t>
+          <t>0507-1408-9011</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로 430 3층</t>
+          <t>인천광역시 중구 신포로27번길 3</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/apecompany</t>
+          <t>https://blog.naver.com/balakas0101</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7553,13 +7553,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>406</v>
+        <v>30</v>
       </c>
       <c r="Q76" t="n">
-        <v>303</v>
+        <v>42</v>
       </c>
       <c r="R76" t="n">
-        <v>709</v>
+        <v>72</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7568,17 +7568,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1479770189</t>
+          <t>16341034</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1479770189</t>
+          <t>https://m.place.naver.com/place/16341034</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
